--- a/education_forms/047_spanish_verb_conjugation_quiz--education_forms.xlsx
+++ b/education_forms/047_spanish_verb_conjugation_quiz--education_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -505,35 +515,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spanish Verb Conjugation Quiz</t>
+          <t>Conjugate the verb 'hablar' in the present tense.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_question</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -556,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_answer</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Conjugate the verb 'comenzar' in the present tense.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,137 +589,137 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_hint</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spanish Verb Conjugation Quiz Hint</t>
+          <t>How would you translate this verb into English?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Please enter a translation.</t>
+          <t>Provide a translation of the verb in the original language.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_question_1</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Conjugate the verb 'hablar' in the present tense.</t>
+          <t>Conjugate the verb 'vivir' in the present tense.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_answer_1</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Answer 1</t>
+          <t>Conjugate the verb 'poder' in the present tense.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_hint_1</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Conjugate the verb 'ser' in the present tense.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_question_2</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conjugate the verb 'comenzar' in the present tense.</t>
+          <t>Conjugate the verb 'ir' in the present tense.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_answer_2</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Answer 2</t>
+          <t>Conjugate the verb 'tener' in the present tense.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -721,18 +731,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_hint_2</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Question 10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Provide the verb in the original language and your translation.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -744,41 +758,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_question_3</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Conjugate the verb 'vivir' in the present tense.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Question 11</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Provide your translation of the verb.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_answer_3</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Answer 3</t>
+          <t>Conjugate the verb 'pensar' in the present tense.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -790,294 +808,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_hint_3</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the correct answer to the following question?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>spanish_verb_conjugation_quiz_question_4</t>
+          <t>question_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Conjugate the verb 'poder' in the present tense.</t>
+          <t>Question 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_answer_4</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Answer 4</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_hint_4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_question_5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Conjugate the verb 'ser' in the present tense.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_answer_5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Answer 5</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_hint_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_question_6</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Conjugate the verb 'ir' in the present tense.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_answer_6</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Answer 6</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_hint_6</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_question_7</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Conjugate the verb 'tener' in the present tense.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_answer_7</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Answer 7</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>spanish_verb_conjugation_quiz_hint_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1087,6 +852,1402 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>question_1_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>hablo_(i_speak)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>hablo (I speak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>question_1_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hableo_(i_speak)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>hableo (I speak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>question_1_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hablo_(hablo)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>hablo (hablo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>question_1_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hablo_(he_speaks)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>hablo (he speaks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>question_1_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>habla_(she/he/it_speaks)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>habla (she/he/it speaks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>habló_(he/she/it_spoke)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>habló (he/she/it spoke)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hablamos_(we_speak)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>hablamos (we speak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hablan_(they_speak)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>hablan (they speak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>hablo_(i_speak)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>hablo (I speak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>hablas_(you_speak)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hablas (you speak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>habla_(he/she/it_speaks)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>habla (he/she/it speaks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>hablábamos_(we_spoke)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hablábamos (we spoke)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>hablás_(you_spoke)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hablás (you spoke)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>hablaron_(they_spoke)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hablaron (they spoke)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>vivo_(i_live)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>vivo (I live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>vivimos_(we_live)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>vivimos (we live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>vivir_(i_live)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>vivir (I live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>vives_(you_live)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>vives (you live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>vive_(he/she/it_lives)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>vive (he/she/it lives)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>vivimos_(they_live)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>vivimos (they live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>vivieron_(we_lived)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>vivieron (we lived)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>vivieron_(you_lived)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>vivieron (you lived)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>vivieron_(he/she/it_lived)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>vivieron (he/she/it lived)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>vivimos_(they_lived)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>vivimos (they lived)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>puedo_(i_can)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>puedo (I can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>podemos_(we_can)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>podemos (we can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pudes_(you_can)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>pudes (you can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>pueden_(you_can)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>pueden (you can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>puedo_(he/she/it_can)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>puedo (he/she/it can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>podían_(they_can)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>podían (they can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>podremos_(we_can)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>podremos (we can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>pude_(you_can)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>pude (you can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>pudieron_(they_can)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>pudieron (they can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>podéis_(you_can)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>podéis (you can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>soy_(i_am)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>soy (I am)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>somos_(we_are)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>somos (we are)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>eres_(you_are)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>eres (you are)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>son_(he/she/it_are)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>son (he/she/it are)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>somos_(they_are)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>somos (they are)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>era_(i_was)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>era (I was)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>hemos_(we_have)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>hemos (we have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>has_(you_have)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>has (you have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>han_(they_have)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>han (they have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>es_(he/she/it_has)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>es (he/she/it has)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>voy_(i_go)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>voy (I go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>vay_(you_go)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>vay (you go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>va_(he/she/it_goes)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>va (he/she/it goes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>vamos_(we_go)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>vamos (we go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>vais_(you_go)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>vais (you go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>vaya_(i_am_going)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>vaya (I am going)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>vayamos_(we_are_going)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>vayamos (we are going)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>vay_(he/she/it_is_going)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>vay (he/she/it is going)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>vayán_(they_are_going)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>vayán (they are going)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>vayamos_(they_are_going)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>vayamos (they are going)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>tengo_(i_have)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>tengo (I have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>tenemos_(we_have)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>tenemos (we have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>tiene_(you_have)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>tiene (you have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>tiene_(he/she/it_has)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>tiene (he/she/it has)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>tengan_(they_have)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>tengan (they have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>tenía_(i_had)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>tenía (I had)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>teníamos_(we_had)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>teníamos (we had)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>tenías_(you_had)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>tenías (you had)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>tenían_(they_had)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>tenían (they had)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>tengo_(he/she/it_had)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>tengo (he/she/it had)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>pienso_(i_think)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>pienso (I think)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>pensamos_(we_think)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>pensamos (we think)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>pienes_(you_think)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>pienes (you think)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>piensas_(you_think)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>piensas (you think)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>piensa_(he/she/it_thinks)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>piensa (he/she/it thinks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>pensamos_(they_think)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>pensamos (they think)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>soy_(i_am)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>soy (I am)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>somos_(we_are)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>somos (we are)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>eres_(you_are)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>eres (you are)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>son_(he/she/it_are)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>son (he/she/it are)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>somos_(they_are)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>somos (they are)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>era_(i_was)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>era (I was)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>hemos_(we_have)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>hemos (we have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>has_(you_have)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>has (you have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>han_(they_have)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>han (they have)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>es_(he/she/it_has)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>es (he/she/it has)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
